--- a/utils/monday_sprint_sprint_2024-45.xlsx
+++ b/utils/monday_sprint_sprint_2024-45.xlsx
@@ -210,7 +210,7 @@
     <t>30/10/2023</t>
   </si>
   <si>
-    <t>09/05/2026</t>
+    <t>04/05/2026</t>
   </si>
   <si>
     <t>Outubro</t>
@@ -366,7 +366,7 @@
     <t>22/08/2024</t>
   </si>
   <si>
-    <t>10/03/2026</t>
+    <t>05/03/2026</t>
   </si>
   <si>
     <t>Agosto</t>
@@ -3374,7 +3374,7 @@
         <v>81</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -3406,7 +3406,7 @@
         <v>21</v>
       </c>
       <c r="Q11">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -3520,7 +3520,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>60</v>
@@ -3534,7 +3534,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>44</v>
@@ -3548,7 +3548,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>113</v>
@@ -3562,7 +3562,7 @@
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>119</v>

--- a/utils/monday_sprint_sprint_2024-45.xlsx
+++ b/utils/monday_sprint_sprint_2024-45.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="189">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>27893</t>
+    <t>7429698378</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,13 +87,13 @@
     <t>13/09/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>15/09/2024</t>
   </si>
   <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
+    <t>Não</t>
   </si>
   <si>
     <t>Semana 2</t>
@@ -102,7 +102,7 @@
     <t>Setembro</t>
   </si>
   <si>
-    <t>26830</t>
+    <t>7438020208</t>
   </si>
   <si>
     <t>Segregação custeiro - Acabamento - Tratamento térmico</t>
@@ -111,37 +111,61 @@
     <t>16/09/2024</t>
   </si>
   <si>
+    <t>24/09/2024</t>
+  </si>
+  <si>
     <t>Fazendo</t>
   </si>
   <si>
     <t>Semana 3</t>
   </si>
   <si>
+    <t>7429694950</t>
+  </si>
+  <si>
     <t>Habilitar cores nos CARDs</t>
   </si>
   <si>
+    <t>7438023681</t>
+  </si>
+  <si>
     <t>Segregação custeiro - Acabamento - Rebarbação</t>
   </si>
   <si>
+    <t>7429704799</t>
+  </si>
+  <si>
     <t>Somar o tempo quando mais de uma operação por cabine</t>
   </si>
   <si>
+    <t>7438024943</t>
+  </si>
+  <si>
     <t>Segregação custeiro - Acabamento - Apoio industrial</t>
   </si>
   <si>
-    <t>27808</t>
+    <t>22/09/2024</t>
+  </si>
+  <si>
+    <t>7428128094</t>
   </si>
   <si>
     <t>Ajustes no sistema de ensaios destrutivos de peças seriadas</t>
   </si>
   <si>
+    <t>7429705994</t>
+  </si>
+  <si>
     <t>Mostrar o nome da operação no campo "OPERANDO"</t>
   </si>
   <si>
+    <t>7429701203</t>
+  </si>
+  <si>
     <t>Aumentar a fonte do campo tempo nos CARDs</t>
   </si>
   <si>
-    <t>27557</t>
+    <t>7333992749</t>
   </si>
   <si>
     <t>Amostras Alto Impacto (Fundição adicional de Seriadas)</t>
@@ -153,9 +177,6 @@
     <t>Feito</t>
   </si>
   <si>
-    <t>Não</t>
-  </si>
-  <si>
     <t>Semana 5</t>
   </si>
   <si>
@@ -171,7 +192,10 @@
     <t>18/09/2024</t>
   </si>
   <si>
-    <t>6090</t>
+    <t>26/09/2024</t>
+  </si>
+  <si>
+    <t>7332179527</t>
   </si>
   <si>
     <t>Analisar as demandas do fluxo de revisão de documentos</t>
@@ -180,6 +204,9 @@
     <t>25310</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Solicitação de serviço</t>
   </si>
   <si>
@@ -204,19 +231,31 @@
     <t>Semana 1</t>
   </si>
   <si>
-    <t>27176</t>
+    <t>7438031928</t>
   </si>
   <si>
     <t>PDI Inspeção, status do laudo.</t>
   </si>
   <si>
+    <t>19/09/2024</t>
+  </si>
+  <si>
+    <t>7438054117</t>
+  </si>
+  <si>
     <t>Ajuste na interface de dados na Inspeção PDI</t>
   </si>
   <si>
+    <t>7438032738</t>
+  </si>
+  <si>
     <t>PDI Relatório de inspeção</t>
   </si>
   <si>
-    <t>26510</t>
+    <t>23/09/2024</t>
+  </si>
+  <si>
+    <t>7429792569</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -225,6 +264,9 @@
     <t>Projeto Sistema PROEX - Finalizar Entrega</t>
   </si>
   <si>
+    <t>28/09/2024</t>
+  </si>
+  <si>
     <t>22986</t>
   </si>
   <si>
@@ -246,7 +288,7 @@
     <t>04/05/2026</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>7436778987</t>
   </si>
   <si>
     <t>AJUSTES CONDIÇÃO DE PAGAMENTO OFERTA / CPC</t>
@@ -255,55 +297,58 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>17/09/2024</t>
+  </si>
+  <si>
+    <t>7437318496</t>
+  </si>
+  <si>
     <t>Interface de visualização de conjuntos</t>
   </si>
   <si>
-    <t>27896</t>
+    <t>7450193305</t>
   </si>
   <si>
     <t>Situação TV Reb VII</t>
   </si>
   <si>
-    <t>17/09/2024</t>
-  </si>
-  <si>
     <t>7454398185</t>
   </si>
   <si>
     <t>Nova Visualização para Modelos Conjunto na Tela de Vinculação de Sequencias</t>
   </si>
   <si>
-    <t>27691</t>
+    <t>7333905438</t>
   </si>
   <si>
     <t>Melhoria Sistema - Materiais Indiretos - MADEIRA PARA MODELOS</t>
   </si>
   <si>
-    <t>27471</t>
+    <t>7334265925</t>
   </si>
   <si>
     <t>Melhorias/Ajustes no Posto de Cópias eletrônico - Melhoria na Pesquisa</t>
   </si>
   <si>
-    <t>27357</t>
+    <t>7359945583</t>
   </si>
   <si>
     <t>Cenário Valorização</t>
   </si>
   <si>
-    <t>27648</t>
+    <t>7437562632</t>
   </si>
   <si>
     <t>APONTAMENTO TABLET MANIPULADORES</t>
   </si>
   <si>
-    <t>27413</t>
+    <t>7334287864</t>
   </si>
   <si>
     <t>Observações Formulário ACVO</t>
   </si>
   <si>
-    <t>27720</t>
+    <t>7372899001</t>
   </si>
   <si>
     <t>Planilha Toto</t>
@@ -312,49 +357,49 @@
     <t>05/09/2024</t>
   </si>
   <si>
-    <t>27857</t>
+    <t>7428087849</t>
   </si>
   <si>
     <t>Novo campo Etiquetas (Sistema Invoice)</t>
   </si>
   <si>
-    <t>27727</t>
+    <t>7372927745</t>
   </si>
   <si>
     <t>REMOVER CPPs BLOQUEADOS</t>
   </si>
   <si>
-    <t>27705</t>
+    <t>7372984933</t>
   </si>
   <si>
     <t>Inclusão da Revisão do Desenho no Planilhão</t>
   </si>
   <si>
-    <t>27855</t>
+    <t>7428103148</t>
   </si>
   <si>
     <t>Preenchimento do cBenef nas notas</t>
   </si>
   <si>
-    <t>27474</t>
+    <t>7436887654</t>
   </si>
   <si>
     <t>Melhorias/Ajustes no Posto de Cópias eletrônico - Gestão dos documentos (Grupos/Cargos)</t>
   </si>
   <si>
-    <t>27778</t>
+    <t>7428188643</t>
   </si>
   <si>
     <t>Melhoria Sistema Embalagens</t>
   </si>
   <si>
-    <t>27752</t>
+    <t>7428230806</t>
   </si>
   <si>
     <t>[COMPRAS] Ajuste tela de planejamento</t>
   </si>
   <si>
-    <t>27864</t>
+    <t>7429862028</t>
   </si>
   <si>
     <t>Correção</t>
@@ -363,19 +408,25 @@
     <t>BUG - Posto de Cópia Eletrônico</t>
   </si>
   <si>
+    <t>7437297488</t>
+  </si>
+  <si>
     <t>Montar e-mail de etapas concluídas na movimentação</t>
   </si>
   <si>
-    <t>27885</t>
+    <t>7428496314</t>
   </si>
   <si>
     <t>Adicionar coluna "Setor seguinte"</t>
   </si>
   <si>
+    <t>7437306354</t>
+  </si>
+  <si>
     <t>Montar rotina para montagens de conjuntos sobre os eventos</t>
   </si>
   <si>
-    <t>27375</t>
+    <t>7360022744</t>
   </si>
   <si>
     <t>Projeto de melhoria - Divergência apontamentos solda</t>
@@ -384,52 +435,55 @@
     <t>Implantação</t>
   </si>
   <si>
-    <t>27561</t>
+    <t>7333972152</t>
   </si>
   <si>
     <t>Criação de Cadastro de Calendário de Máquina para Cálculo de IROG</t>
   </si>
   <si>
-    <t>Solicito a abertura de chamado para criação de tela de cadastro no sistema que possibilite a criação de calendário de máquinas para cálculo de IROG, segue abaixo modelo utilizado no EFACT: Conforme acordado em reunião (22/08) é necessário que haja uma funcionalidade no calendário que permita que o c</t>
-  </si>
-  <si>
-    <t>Guilherme Mendes</t>
-  </si>
-  <si>
-    <t>05/03/2026</t>
+    <t>7437727267</t>
   </si>
   <si>
     <t>Criação de Cadastro de Calendário de Máquina para Cálculo de IROG - Criar Tabelas</t>
   </si>
   <si>
+    <t>7429685814</t>
+  </si>
+  <si>
     <t>Permitir o apontamento de apenas 1 sequencia por cabine para mais de 1 operador</t>
   </si>
   <si>
+    <t>7429685165</t>
+  </si>
+  <si>
     <t>Listar modelos e tempos padrões para o centro de custos 1480</t>
   </si>
   <si>
+    <t>7429686275</t>
+  </si>
+  <si>
     <t>Enviar o nome da operação no campo para a MDL_TempoSeq</t>
   </si>
   <si>
-    <t>26505</t>
+    <t>7429772131</t>
   </si>
   <si>
     <t>WMS - Adequação SPS</t>
   </si>
   <si>
-    <t>27892</t>
+    <t>7429272873</t>
   </si>
   <si>
     <t>Janelas de Pagamento - Alteração Integração Benner</t>
   </si>
   <si>
-    <t>27772</t>
+    <t>7445499463</t>
   </si>
   <si>
     <t>ALTERAÇÃO TELA CONFERENCIA DE NOTA FISCAL - SISTEMA DEPOSITO</t>
   </si>
   <si>
-    <t>27954</t>
+    <t>7454351552</t>
   </si>
   <si>
     <t>Sisitema de apontamento de solda Digital tablet</t>
@@ -447,7 +501,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-45</t>
+    <t>Ago/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -499,6 +553,9 @@
   </si>
   <si>
     <t>Sim</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
   </si>
   <si>
     <t>Abertos</t>
@@ -1083,16 +1140,16 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>28</v>
@@ -1100,7 +1157,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1112,10 +1169,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1147,7 +1204,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1159,10 +1216,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1177,16 +1234,16 @@
         <v>31</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>28</v>
@@ -1194,7 +1251,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1206,10 +1263,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1241,7 +1298,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1253,10 +1310,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1271,16 +1328,16 @@
         <v>31</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -1288,7 +1345,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1300,10 +1357,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1335,7 +1392,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1347,10 +1404,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1382,7 +1439,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1394,10 +1451,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1429,7 +1486,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1441,10 +1498,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1456,27 +1513,27 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1488,10 +1545,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1503,19 +1560,19 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>28</v>
@@ -1523,34 +1580,34 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>24</v>
@@ -1562,42 +1619,42 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>24</v>
@@ -1609,7 +1666,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1617,7 +1674,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1629,10 +1686,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1647,16 +1704,16 @@
         <v>31</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -1664,7 +1721,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1676,10 +1733,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1694,16 +1751,16 @@
         <v>31</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -1711,7 +1768,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1723,10 +1780,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1741,16 +1798,16 @@
         <v>31</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -1758,22 +1815,22 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1788,13 +1845,13 @@
         <v>23</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>27</v>
@@ -1805,37 +1862,37 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1852,7 +1909,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1864,13 +1921,13 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>21</v>
@@ -1882,16 +1939,16 @@
         <v>31</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -1899,7 +1956,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1911,13 +1968,13 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>21</v>
@@ -1929,16 +1986,16 @@
         <v>31</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>28</v>
@@ -1946,7 +2003,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1958,10 +2015,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1973,19 +2030,19 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L22" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>28</v>
@@ -1993,7 +2050,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2005,10 +2062,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2020,19 +2077,19 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>28</v>
@@ -2040,7 +2097,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2052,10 +2109,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2067,27 +2124,27 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2099,10 +2156,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2114,27 +2171,27 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2146,10 +2203,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2161,19 +2218,19 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>28</v>
@@ -2181,7 +2238,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2193,10 +2250,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2211,16 +2268,16 @@
         <v>31</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>28</v>
@@ -2228,7 +2285,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2240,10 +2297,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2255,27 +2312,27 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2287,10 +2344,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2302,19 +2359,19 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>28</v>
@@ -2322,7 +2379,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2334,10 +2391,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2352,13 +2409,13 @@
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>27</v>
@@ -2369,7 +2426,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2381,10 +2438,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2396,19 +2453,19 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>28</v>
@@ -2416,7 +2473,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2428,10 +2485,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2443,19 +2500,19 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>28</v>
@@ -2463,7 +2520,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2475,10 +2532,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2493,13 +2550,13 @@
         <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>27</v>
@@ -2510,7 +2567,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2522,10 +2579,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2540,16 +2597,16 @@
         <v>31</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -2557,7 +2614,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2569,10 +2626,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2587,13 +2644,13 @@
         <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>27</v>
@@ -2604,7 +2661,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2616,10 +2673,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2634,13 +2691,13 @@
         <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>27</v>
@@ -2651,22 +2708,22 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2681,13 +2738,13 @@
         <v>23</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>27</v>
@@ -2698,7 +2755,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2710,13 +2767,13 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>21</v>
@@ -2728,16 +2785,16 @@
         <v>31</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>28</v>
@@ -2745,7 +2802,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2757,10 +2814,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2775,13 +2832,13 @@
         <v>23</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>27</v>
@@ -2792,7 +2849,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2804,13 +2861,13 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>21</v>
@@ -2822,16 +2879,16 @@
         <v>31</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>28</v>
@@ -2839,22 +2896,22 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2866,19 +2923,19 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>28</v>
@@ -2886,7 +2943,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2895,45 +2952,45 @@
         <v>17</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O42" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2942,37 +2999,37 @@
         <v>17</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>28</v>
@@ -2980,7 +3037,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>15</v>
+        <v>144</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -2992,10 +3049,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3010,13 +3067,13 @@
         <v>23</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>27</v>
@@ -3027,7 +3084,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3039,10 +3096,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3057,13 +3114,13 @@
         <v>23</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>27</v>
@@ -3074,7 +3131,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>15</v>
+        <v>148</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3086,10 +3143,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3104,13 +3161,13 @@
         <v>23</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>27</v>
@@ -3121,7 +3178,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3133,10 +3190,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3151,13 +3208,13 @@
         <v>23</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>27</v>
@@ -3168,7 +3225,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3180,13 +3237,13 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>21</v>
@@ -3198,13 +3255,13 @@
         <v>23</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>27</v>
@@ -3215,7 +3272,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3227,10 +3284,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3242,19 +3299,19 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K49" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="K49" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L49" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>28</v>
@@ -3262,7 +3319,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3274,34 +3331,34 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L50" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="M50" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>28</v>
@@ -3309,7 +3366,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3321,10 +3378,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3336,19 +3393,19 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>28</v>
@@ -3367,23 +3424,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="E2" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3391,16 +3448,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3411,20 +3468,20 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>544</v>
+        <v>12.28</v>
       </c>
       <c r="J5" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K22">
         <v>27</v>
@@ -3432,7 +3489,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="K23">
         <v>9</v>
@@ -3440,7 +3497,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3471,12 +3528,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="B2">
         <v>50</v>
@@ -3490,35 +3547,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>544</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3526,7 +3583,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -3535,54 +3592,54 @@
         <v>46</v>
       </c>
       <c r="G10" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="N10">
         <v>27</v>
       </c>
       <c r="P10" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="Q10">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="H11">
         <v>5</v>
       </c>
       <c r="J11" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="K11">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="M11" t="s">
         <v>25</v>
@@ -3591,15 +3648,21 @@
         <v>9</v>
       </c>
       <c r="P11" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="Q11">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -3611,53 +3674,41 @@
         <v>43</v>
       </c>
       <c r="J12" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="K12">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
-      <c r="P12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q12">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H13">
         <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
-      <c r="P13" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q13">
-        <v>4</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="N14">
         <v>9</v>
@@ -3665,7 +3716,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3673,7 +3724,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3681,7 +3732,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3689,10 +3740,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3700,7 +3751,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3708,142 +3759,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>537</v>
+        <v>642</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>124</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>521</v>
+        <v>642</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
